--- a/review/etnografiya/may-december/may/may.xlsx
+++ b/review/etnografiya/may-december/may/may.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда гость переступает порог двора?</t>
+          <t xml:space="preserve">Гость и хозяин проходят одну калитку, но идут разными путями. Маленькая граница двора открывает порядок соседства и домашнего труда.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему сани нельзя просто поставить на колёса?</t>
+          <t xml:space="preserve">Телега отличается от саней не только колёсами. Летний путь требует другой опоры и размещения груза — устройство меняется вместе с дорогой.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -162,7 +162,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что первым замечаешь в мужской рубахе?</t>
+          <t xml:space="preserve">Застёжка косоворотки смещена в сторону. Небольшая деталь сразу меняет вид рубахи и помогает различить крой, не придумывая единую историю его появления.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как поднять руки в рубахе из прямых полотнищ?</t>
+          <t xml:space="preserve">Небольшой лоскут под рукавом даёт свободу движения. Ластовица показывает, как точная деталь меняет удобство рубахи из прямых полотнищ.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что нужно взять человеку, который уйдёт со стадом на весь день?</t>
+          <t xml:space="preserve">Пастух уходит со стадом на целый день. Его сумка собирает нужное вдали от дома — каждый предмет занимает место ради конкретного дела.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -243,7 +243,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему начало выпаса становилось событием для деревни?</t>
+          <t xml:space="preserve">Первый выход стада становится событием деревни. В обычаях Егорьева дня сезонный труд соединяется с заботой людей о благополучии хозяйства.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли услышать, где пасётся твоя корова?</t>
+          <t xml:space="preserve">Корова скрылась из виду, но ботало выдаёт её движение. Маленькая звучащая вещь помогает человеку следить за стадом на расстоянии.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как двор помогает заботиться о домашних птицах?</t>
+          <t xml:space="preserve">Для птицы во дворе отводят гнездо, корм и воду. Небольшой участок хозяйства показывает, сколько ежедневного внимания требует домашняя живность.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие следы большого события остаются в домашнем альбоме?</t>
+          <t xml:space="preserve">Большая Победа остаётся в семейном альбоме. Снимок сохраняет лица, а подписи и воспоминания возвращают имена людей и обстоятельства встречи.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как прямоугольные полотнища становятся просторной одеждой?</t>
+          <t xml:space="preserve">Прямоугольные полотнища собираются в просторный сарафан. Объём рождается из сборки ткани — сложный силуэт начинается с простых частей.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли расширить подол, сохранив узкий верх?</t>
+          <t xml:space="preserve">Клинья расширяют подол, оставляя верх узким. В косоклинном сарафане мастерство кроя видно по тому, как распределяется ткань в движении.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как многослойность меняет весь костюм?</t>
+          <t xml:space="preserve">Короткая душегрея меняет вид длинного сарафана. Костюм складывается слоями: одна вещь задаёт новый силуэт всему наряду.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -432,7 +432,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рабочая вещь могла стать нарядной?</t>
+          <t xml:space="preserve">Передник защищает одежду и несёт отделку. Рабочая вещь может стать нарядной — местная традиция соединяет пользу с вниманием к красоте.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -459,7 +459,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как небольшая деталь меняет причёску?</t>
+          <t xml:space="preserve">Косник держится на конце девичьей косы. Маленькое украшение рассчитано на конкретное место: крепление объясняет форму не хуже узора.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что скрывается за одним названием?</t>
+          <t xml:space="preserve">За названием «сорока» скрывается убор из нескольких частей. Каждый слой делает свою работу, прежде чем появится знакомый нарядный силуэт.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему украшение интересно рассматривать не только спереди?</t>
+          <t xml:space="preserve">Подвесы нагрудного украшения видны сбоку и в движении. Наряд устроен объёмно: способ крепления хранит часть мастерского замысла.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как покупной материал меняет привычную рубаху?</t>
+          <t xml:space="preserve">Покупной кумач входит в деревенскую одежду. Новый материал меняет поверхность привычной рубахи, сохраняя связь обновления с местным костюмом.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какая ткань выдавала стремление одеться модно?</t>
+          <t xml:space="preserve">Плис придаёт нарядным штанам особую поверхность. Молодёжная мода читается в фактуре ткани, которую трудно заметить издали.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В какой момент городской силуэт становится деревенским?</t>
+          <t xml:space="preserve">Кофта и юбка составляют «парочку». Новый силуэт входит в местный гардероб — история деревенской одежды продолжается через перемены кроя.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли один платок выглядеть как три разные вещи?</t>
+          <t xml:space="preserve">Один квадратный платок можно сложить и надеть по-разному. Движение рук меняет силуэт вещи без единого нового шва.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему этот день нельзя навсегда поставить на 21 мая?</t>
+          <t xml:space="preserve">Вознесение зависит от даты Пасхи и не закреплено за одним числом мая. Подвижный праздник показывает другой способ устроить годовой круг.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как одна память соединяла разные занятия людей?</t>
+          <t xml:space="preserve">Никола вешний входит в хозяйственный календарь разных мест. Один праздничный день связывает церковную память с конкретными занятиями людей.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что рассказывает подошва о работе мастера?</t>
+          <t xml:space="preserve">Подошва прячет работу сапожника от первого взгляда. Гвозди и швы показывают, каким способом мастер удержал вместе части обуви.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как научиться читать, если книг совсем немного?</t>
+          <t xml:space="preserve">Домашняя азбука превращает буквы в освоенное умение. Одна страница хранит путь от узнавания знака к слову, которое ребёнок читает сам.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли понять работу замка, не сломав его?</t>
+          <t xml:space="preserve">Поворот ключа двигает скрытый запор. Медный замок соединяет небольшое движение руки с защитой вещей, которым хозяин отвёл особое место.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что держит створку годами?</t>
+          <t xml:space="preserve">Тяжёлая дверь держится на кованых петлях. Длинная металлическая полоса распределяет крепление — кузнечная работа остаётся в ежедневном движении створки.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как небольшая скамья становится местом общения?</t>
+          <t xml:space="preserve">Лавка у дома собирает соседей. Простая скамья становится местом обмена новостями, когда люди задерживаются рядом и обращаются друг к другу.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему берёза появляется в рассказах о начале лета?</t>
+          <t xml:space="preserve">Берёзовые ветви входят в семицкий обряд. Зелёный материал становится частью праздничного действия, порядок которого различается от места к месту.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как несколько изгибов превращаются в бегущую лошадь?</t>
+          <t xml:space="preserve">Несколько изгибов кисти создают городецкого коня. Движение животного читается в силуэте ещё до появления мелких деталей нарядной росписи.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли продолжить узор, не зная его названия?</t>
+          <t xml:space="preserve">Красный и чёрный складываются в повторяющийся ряд. Мезенская роспись держит ритм узора: следующий элемент связан с уже написанными.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется в знакомом интерьере в праздничный день?</t>
+          <t xml:space="preserve">На Троицу привычный дом получает зелёное убранство. Местный обычай делает праздник видимым внутри повседневного семейного пространства.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
